--- a/testprocess/1-process/db-test-plan.xlsx
+++ b/testprocess/1-process/db-test-plan.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="97">
   <si>
     <t>主要进行1.8版本功能测试</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -402,10 +402,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>预计下周开始</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>ci中python测试结果不正确，需要修改测试用例</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -419,6 +415,14 @@
   </si>
   <si>
     <t>本周内完成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>这周开始</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>这周开始，预计2014-08-05评审</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1494,7 +1498,7 @@
         <v>11</v>
       </c>
       <c r="E53" s="13" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -1536,7 +1540,7 @@
         <v>33</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -1546,11 +1550,11 @@
       <c r="C57" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="D57" s="10" t="s">
-        <v>33</v>
+      <c r="D57" s="8" t="s">
+        <v>11</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -1560,11 +1564,11 @@
       <c r="C58" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D58" s="10" t="s">
-        <v>33</v>
+      <c r="D58" s="8" t="s">
+        <v>11</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -1611,7 +1615,7 @@
     </row>
     <row r="62" spans="1:5">
       <c r="B62" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C62" s="6" t="s">
         <v>10</v>
@@ -1620,7 +1624,7 @@
         <v>11</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>

--- a/testprocess/1-process/db-test-plan.xlsx
+++ b/testprocess/1-process/db-test-plan.xlsx
@@ -4,11 +4,11 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="sequoiadb-plan" sheetId="1" r:id="rId1"/>
-    <sheet name="测试用例补充" sheetId="2" r:id="rId2"/>
+    <sheet name="测试用例维护" sheetId="2" r:id="rId2"/>
     <sheet name="未完成的功能性测试" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="90">
   <si>
     <t>主要进行1.8版本功能测试</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -91,50 +91,6 @@
   </si>
   <si>
     <t>10.分区键联合索引</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>自动化测试用例补充</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>java连接池</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>刘武兴</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>还差部分异常测试用例</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>collection-alter</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>丁普升</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>需要补充自动化测试用例</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>java驱动测试用例</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>需要整体测试</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>explain</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>联合索引、分区键</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -423,6 +379,22 @@
   </si>
   <si>
     <t>这周开始，预计2014-08-05评审</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试用例维护</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ci中python驱动测试用例</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>js测试用例主机名、端口号用变量的问题</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>js测试用例中transaction用例</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -993,7 +965,7 @@
         <v>10</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1004,7 +976,7 @@
         <v>5</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15.75" customHeight="1">
@@ -1018,7 +990,7 @@
         <v>9</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1029,7 +1001,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1043,7 +1015,7 @@
         <v>11</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1054,7 +1026,7 @@
         <v>2</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="27">
@@ -1084,13 +1056,13 @@
         <v>18</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="D11" s="9" t="s">
         <v>9</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -1099,30 +1071,30 @@
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="10" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="141" customHeight="1">
       <c r="B13" s="5" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="D13" s="9" t="s">
         <v>9</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="B14" s="5" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="10" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1130,21 +1102,21 @@
         <v>41827</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="54">
       <c r="B18" s="5" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="10" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="B19" s="5" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>8</v>
@@ -1155,7 +1127,7 @@
     </row>
     <row r="20" spans="1:5">
       <c r="B20" s="5" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>2</v>
@@ -1166,7 +1138,7 @@
     </row>
     <row r="21" spans="1:5" ht="27">
       <c r="B21" s="5" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>8</v>
@@ -1175,12 +1147,12 @@
         <v>11</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="B22" s="5" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>15</v>
@@ -1192,7 +1164,7 @@
     <row r="23" spans="1:5">
       <c r="A23" s="11"/>
       <c r="B23" s="5" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>5</v>
@@ -1203,10 +1175,10 @@
     </row>
     <row r="24" spans="1:5" ht="27">
       <c r="B24" s="5" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="D24" s="8" t="s">
         <v>11</v>
@@ -1214,7 +1186,7 @@
     </row>
     <row r="25" spans="1:5">
       <c r="B25" s="5" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>8</v>
@@ -1231,26 +1203,26 @@
         <v>41834</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="54">
       <c r="B29" s="5" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="B30" s="5" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>2</v>
@@ -1261,7 +1233,7 @@
     </row>
     <row r="31" spans="1:5">
       <c r="B31" s="5" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>15</v>
@@ -1272,7 +1244,7 @@
     </row>
     <row r="32" spans="1:5">
       <c r="B32" s="5" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>5</v>
@@ -1281,15 +1253,15 @@
         <v>9</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="27">
       <c r="B33" s="5" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="D33" s="8" t="s">
         <v>11</v>
@@ -1297,7 +1269,7 @@
     </row>
     <row r="34" spans="1:5">
       <c r="B34" s="5" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="C34" s="6" t="s">
         <v>8</v>
@@ -1308,35 +1280,35 @@
     </row>
     <row r="35" spans="1:5">
       <c r="B35" s="5" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="B36" s="5" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="C36" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="B37" s="5" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="C37" s="6" t="s">
         <v>8</v>
@@ -1350,12 +1322,12 @@
         <v>41841</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="54">
       <c r="B41" s="5" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>2</v>
@@ -1364,12 +1336,12 @@
         <v>11</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="B42" s="14" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="C42" s="6" t="s">
         <v>5</v>
@@ -1378,26 +1350,26 @@
         <v>11</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="27">
       <c r="B43" s="5" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="D43" s="9" t="s">
         <v>9</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="B44" s="14" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C44" s="6" t="s">
         <v>2</v>
@@ -1406,12 +1378,12 @@
         <v>11</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="B45" s="5" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="C45" s="6" t="s">
         <v>2</v>
@@ -1420,12 +1392,12 @@
         <v>9</v>
       </c>
       <c r="E45" s="15" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="B46" s="5" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="C46" s="6" t="s">
         <v>8</v>
@@ -1434,40 +1406,40 @@
         <v>9</v>
       </c>
       <c r="E46" s="16" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="B47" s="5" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="D47" s="10" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="27">
       <c r="B48" s="5" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="D48" s="10" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="B49" s="5" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="C49" s="6" t="s">
         <v>8</v>
@@ -1476,7 +1448,7 @@
         <v>9</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -1484,12 +1456,12 @@
         <v>41848</v>
       </c>
       <c r="B52" s="12" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="54">
       <c r="B53" s="5" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="C53" s="6" t="s">
         <v>2</v>
@@ -1498,12 +1470,12 @@
         <v>11</v>
       </c>
       <c r="E53" s="13" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="B54" s="14" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="C54" s="6" t="s">
         <v>5</v>
@@ -1512,12 +1484,12 @@
         <v>11</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="B55" s="14" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="C55" s="6" t="s">
         <v>2</v>
@@ -1526,26 +1498,26 @@
         <v>11</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="B56" s="5" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="C56" s="6" t="s">
         <v>5</v>
       </c>
       <c r="D56" s="10" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="B57" s="5" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="C57" s="6" t="s">
         <v>5</v>
@@ -1554,12 +1526,12 @@
         <v>11</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="B58" s="5" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="C58" s="6" t="s">
         <v>2</v>
@@ -1568,40 +1540,40 @@
         <v>11</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="B59" s="5" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="D59" s="10" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="27">
       <c r="B60" s="5" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="D60" s="10" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="B61" s="5" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="C61" s="6" t="s">
         <v>10</v>
@@ -1610,12 +1582,12 @@
         <v>11</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="B62" s="5" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="C62" s="6" t="s">
         <v>10</v>
@@ -1624,7 +1596,7 @@
         <v>11</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -1640,7 +1612,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="16.75" customWidth="1"/>
@@ -1648,52 +1620,28 @@
     <col min="5" max="5" width="26.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:4">
       <c r="A1" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="B2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D2" s="4">
-        <v>41820</v>
-      </c>
-      <c r="E2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+        <v>87</v>
+      </c>
+      <c r="D2" s="4"/>
+    </row>
+    <row r="3" spans="1:4">
       <c r="B3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D3" s="4">
-        <v>41820</v>
-      </c>
-      <c r="E3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+        <v>88</v>
+      </c>
+      <c r="D3" s="4"/>
+    </row>
+    <row r="4" spans="1:4">
       <c r="B4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" s="4">
-        <v>41820</v>
-      </c>
-      <c r="E4" t="s">
-        <v>27</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="D4" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -1704,26 +1652,16 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="16.25" customWidth="1"/>
     <col min="2" max="2" width="18.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:1">
       <c r="A1" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="B2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="B3" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/testprocess/1-process/db-test-plan.xlsx
+++ b/testprocess/1-process/db-test-plan.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="2"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
     <sheet name="sequoiadb-plan" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="91">
   <si>
     <t>主要进行1.8版本功能测试</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -370,10 +370,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>本周内完成</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>这周开始</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -395,6 +391,14 @@
   </si>
   <si>
     <t>js测试用例中transaction用例</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>已经测试完成hadoop2.2与sequoiadb的对接，成功</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11.CI中js测试用例错误定位、修改</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -927,7 +931,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E62"/>
+  <dimension ref="A1:E63"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="11.625" style="2" customWidth="1"/>
@@ -1526,7 +1530,7 @@
         <v>11</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -1540,7 +1544,7 @@
         <v>11</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -1592,11 +1596,22 @@
       <c r="C62" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D62" s="8" t="s">
+      <c r="D62" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="B63" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="C63" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D63" s="8" t="s">
         <v>11</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -1622,24 +1637,24 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="B2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D2" s="4"/>
     </row>
     <row r="3" spans="1:4">
       <c r="B3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D3" s="4"/>
     </row>
     <row r="4" spans="1:4">
       <c r="B4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D4" s="4"/>
     </row>

--- a/testprocess/1-process/db-test-plan.xlsx
+++ b/testprocess/1-process/db-test-plan.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="92">
   <si>
     <t>主要进行1.8版本功能测试</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -394,11 +394,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>已经测试完成hadoop2.2与sequoiadb的对接，成功</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>11.CI中js测试用例错误定位、修改</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>已经测试完成hadoop2.2与sequoiadb的对接，成功；已经测试完成hadoop1.2.1与sequoiadb的对接，成功。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>已经将subCL拆分为10个小的测试用例。部分测试用例并发执行时没有处理cs、cl创建失败的异常</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1512,8 +1516,8 @@
       <c r="C56" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="D56" s="10" t="s">
-        <v>22</v>
+      <c r="D56" s="9" t="s">
+        <v>9</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>80</v>
@@ -1600,18 +1604,21 @@
         <v>9</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="B63" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C63" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D63" s="8" t="s">
         <v>11</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>91</v>
       </c>
     </row>
   </sheetData>

--- a/testprocess/1-process/db-test-plan.xlsx
+++ b/testprocess/1-process/db-test-plan.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="104">
   <si>
     <t>主要进行1.8版本功能测试</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -362,10 +362,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>计划在svn中重新创建一个有关静态库测试的项目，利用以前的测试用例代码，但是修改编译的scons文件，使其链接静态链接库。最后需要CI做些调整</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>10.powerpc上sequoiadb与hadoop的对接</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -403,6 +399,82 @@
   </si>
   <si>
     <t>已经将subCL拆分为10个小的测试用例。部分测试用例并发执行时没有处理cs、cl创建失败的异常</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">计划在svn中重新创建一个有关静态库测试的项目，利用以前的测试用例代码，但是修改编译的scons文件，使其链接静态链接库。最后需要CI做些调整
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>已经完成</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>scons文件，并且CI上运行通过。但是在测试报告上没有反应</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试实现</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试实现，</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.包含很多节点集群的随机启动</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2.滚动升级测试计划</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.数据一致性测试设计</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4.lob对象测试设计</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>本周二评审</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5.ci中测试用例执行状态收集</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6.ci改进：整体测试活动中，无关系的构建项目应该不会彼此受到影响</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7.有关场景测试计划和设计</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8.CI中js测试用例错误定位、修改</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目前测试用例错误数目已经减少至10个左右。大部分是并发测试场景错误</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -410,7 +482,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="6">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -455,6 +527,29 @@
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0070C0"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0070C0"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="7">
@@ -526,7 +621,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -571,6 +666,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -935,7 +1033,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E63"/>
+  <dimension ref="A1:E74"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="11.625" style="2" customWidth="1"/>
@@ -1474,11 +1572,11 @@
       <c r="C53" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D53" s="8" t="s">
-        <v>11</v>
+      <c r="D53" s="9" t="s">
+        <v>9</v>
       </c>
       <c r="E53" s="13" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -1534,7 +1632,7 @@
         <v>11</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -1548,7 +1646,7 @@
         <v>11</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -1595,7 +1693,7 @@
     </row>
     <row r="62" spans="1:5">
       <c r="B62" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C62" s="6" t="s">
         <v>10</v>
@@ -1604,12 +1702,12 @@
         <v>9</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="B63" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C63" s="6" t="s">
         <v>10</v>
@@ -1618,7 +1716,124 @@
         <v>11</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="11">
+        <v>41855</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="B67" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="C67" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D67" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="B68" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="C68" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D68" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="B69" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="C69" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D69" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="B70" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="C70" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D70" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="B71" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C71" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D71" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" ht="27">
+      <c r="B72" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="C72" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D72" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="B73" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="C73" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D73" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="B74" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="C74" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D74" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>103</v>
       </c>
     </row>
   </sheetData>
@@ -1644,24 +1859,24 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="B2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D2" s="4"/>
     </row>
     <row r="3" spans="1:4">
       <c r="B3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D3" s="4"/>
     </row>
     <row r="4" spans="1:4">
       <c r="B4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D4" s="4"/>
     </row>

--- a/testprocess/1-process/db-test-plan.xlsx
+++ b/testprocess/1-process/db-test-plan.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="106">
   <si>
     <t>主要进行1.8版本功能测试</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -475,6 +475,14 @@
   </si>
   <si>
     <t>目前测试用例错误数目已经减少至10个左右。大部分是并发测试场景错误</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9.CI中获取js测试用例脚本执行的输出</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目前js测试用例错误，大部分都是并发场景下的错误。这些用例非并发下执行正确。由于无法获取当时js脚本的输出，不能定位错误，所以不方便进行调试</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1033,7 +1041,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E74"/>
+  <dimension ref="A1:E75"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="11.625" style="2" customWidth="1"/>
@@ -1834,6 +1842,20 @@
       </c>
       <c r="E74" s="2" t="s">
         <v>103</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="B75" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="C75" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D75" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>105</v>
       </c>
     </row>
   </sheetData>

--- a/testprocess/1-process/db-test-plan.xlsx
+++ b/testprocess/1-process/db-test-plan.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="110">
   <si>
     <t>主要进行1.8版本功能测试</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -483,6 +483,22 @@
   </si>
   <si>
     <t>目前js测试用例错误，大部分都是并发场景下的错误。这些用例非并发下执行正确。由于无法获取当时js脚本的输出，不能定位错误，所以不方便进行调试</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11.ant测试用例缺少sdbkillmasternode</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10.CI中驱动用例需要在集群环境下运行</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目前驱动测试用例仅在standalone场景下执行，这是远远不够的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://192.168.20.11/sequoiadb/trunk/testcases/hlt/ant_testcases/ant/transaction_exception_handle/trans_kill_master.xml中调用了sdbkillmasternode方法，但是实际ant并没有实现这个方法</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -629,7 +645,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -676,6 +692,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1041,7 +1060,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E75"/>
+  <dimension ref="A1:E77"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="11.625" style="2" customWidth="1"/>
@@ -1858,14 +1877,43 @@
         <v>105</v>
       </c>
     </row>
+    <row r="76" spans="1:5">
+      <c r="B76" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="C76" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D76" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" ht="40.5">
+      <c r="B77" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="C77" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D77" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E77" s="18" t="s">
+        <v>109</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="E46" r:id="rId1" display="http://jira:8080/browse/SEQUOIADBMAINSTREAM-257"/>
     <hyperlink ref="E45" r:id="rId2" display="http://jira:8080/browse/SEQUOIADBMAINSTREAM-264"/>
+    <hyperlink ref="E77" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId4"/>
 </worksheet>
 </file>
 

--- a/testprocess/1-process/db-test-plan.xlsx
+++ b/testprocess/1-process/db-test-plan.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="114">
   <si>
     <t>主要进行1.8版本功能测试</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -499,6 +499,22 @@
   </si>
   <si>
     <t>http://192.168.20.11/sequoiadb/trunk/testcases/hlt/ant_testcases/ant/transaction_exception_handle/trans_kill_master.xml中调用了sdbkillmasternode方法，但是实际ant并没有实现这个方法</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12.sdbsupport工具能否对外提供使用</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>安装包是否包含、信息中心文档是否有使用说明、jira中问题是否关闭</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13.联合索引时查询匹配操作符的测试用例</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>根据SEQUOIADBMAINSTREAM-293，需要对其它查询操作符也进行测试</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1060,7 +1076,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E77"/>
+  <dimension ref="A1:E79"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="11.625" style="2" customWidth="1"/>
@@ -1903,6 +1919,34 @@
       </c>
       <c r="E77" s="18" t="s">
         <v>109</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="B78" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="C78" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D78" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="B79" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="C79" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D79" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>113</v>
       </c>
     </row>
   </sheetData>

--- a/testprocess/1-process/db-test-plan.xlsx
+++ b/testprocess/1-process/db-test-plan.xlsx
@@ -720,74 +720,6 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -799,7 +731,7 @@
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="C7EDCC"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -1306,8 +1238,8 @@
       <c r="C22" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D22" s="8" t="s">
-        <v>11</v>
+      <c r="D22" s="9" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1329,8 +1261,8 @@
       <c r="C24" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="D24" s="8" t="s">
-        <v>11</v>
+      <c r="D24" s="9" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1412,8 +1344,8 @@
       <c r="C33" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="D33" s="8" t="s">
-        <v>11</v>
+      <c r="D33" s="9" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -1565,8 +1497,8 @@
       <c r="C47" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="D47" s="10" t="s">
-        <v>22</v>
+      <c r="D47" s="8" t="s">
+        <v>11</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>63</v>
@@ -1579,8 +1511,8 @@
       <c r="C48" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="D48" s="10" t="s">
-        <v>22</v>
+      <c r="D48" s="8" t="s">
+        <v>11</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>66</v>
@@ -1699,8 +1631,8 @@
       <c r="C59" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="D59" s="10" t="s">
-        <v>22</v>
+      <c r="D59" s="8" t="s">
+        <v>11</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>63</v>
@@ -1713,8 +1645,8 @@
       <c r="C60" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="D60" s="10" t="s">
-        <v>22</v>
+      <c r="D60" s="8" t="s">
+        <v>11</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>66</v>
@@ -1844,8 +1776,8 @@
       <c r="C72" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="D72" s="10" t="s">
-        <v>22</v>
+      <c r="D72" s="8" t="s">
+        <v>11</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>66</v>

--- a/testprocess/1-process/db-test-plan.xlsx
+++ b/testprocess/1-process/db-test-plan.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="131">
   <si>
     <t>主要进行1.8版本功能测试</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -375,10 +375,6 @@
   </si>
   <si>
     <t>测试用例维护</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ci中python驱动测试用例</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -430,10 +426,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>测试实现</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>测试实现，</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -454,10 +446,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>本周二评审</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>5.ci中测试用例执行状态收集</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -515,6 +503,138 @@
   </si>
   <si>
     <t>根据SEQUOIADBMAINSTREAM-293，需要对其它查询操作符也进行测试</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试计划评审完成，开始测试实现</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>暂停</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试设计评审通过，测试用例完成。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.cluster nodes random-start</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试实现，待数据一致性工具测试完成再进行 集群节点随机启动测试</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2.rolling-update</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试实现，待lob测试完成后再进行</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.数据一致性测试执行</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>完成基本功能测试，需要验证在数据量比较多的情况下执行效率</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>本周二评审，但是评审未通过，下周需要再次评审</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试设计，本周进行第二次评审</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ci中python驱动测试用例</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>将测试用例执行起止时间、执行所需时间、执行结果收集记录在数据库中，以供后续分析</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>案例、场景、环境？Sql、集群、故障？脚本、工具、程序？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>例如现在CI测试包括驱动测试、js测试。很多情况下驱动测试用例编译失败导致整个测试活动失败，后续js测试根本没有运行。希望能做到驱动测试的构建失败，不影响后续js测试。在测试报告中记录驱动测试没过就可以</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>例如现在CI测试包括驱动测试、js测试。很多情况下驱动测试用例编译失败导致整个测试活动失败，后续js测试根本没有运行。希望能做到驱动测试的构建失败，不影响后续js测试。在测试报告中记录驱动测试没过就可以</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目前js测试用例错误，大部分都是并发场景下的错误。这些用例非并发下执行正确。由于无法获取当时js脚本的输出，不能定位错误，所以不方便进行调试</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>安装包已经包含</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>信息中心文档没有使用说明</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>jira中问题已经关闭</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13.rpm安装包测试</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>14.CI集成rpm包</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -522,7 +642,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="9">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -591,8 +711,31 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1" tint="0.499984740745262"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -629,6 +772,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7030A0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -661,7 +810,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -713,6 +862,13 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -720,6 +876,74 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -731,7 +955,7 @@
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr val="window" lastClr="C7EDCC"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -1008,7 +1232,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E79"/>
+  <dimension ref="A1:E96"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="11.625" style="2" customWidth="1"/>
@@ -1551,7 +1775,7 @@
         <v>9</v>
       </c>
       <c r="E53" s="13" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -1677,12 +1901,12 @@
         <v>9</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="B63" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C63" s="6" t="s">
         <v>10</v>
@@ -1691,7 +1915,7 @@
         <v>11</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -1701,7 +1925,7 @@
     </row>
     <row r="67" spans="1:5">
       <c r="B67" s="17" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C67" s="6" t="s">
         <v>5</v>
@@ -1710,40 +1934,40 @@
         <v>11</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="B68" s="17" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C68" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D68" s="8" t="s">
-        <v>11</v>
+      <c r="D68" s="9" t="s">
+        <v>9</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>92</v>
+        <v>111</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="B69" s="14" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C69" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="D69" s="8" t="s">
-        <v>11</v>
+      <c r="D69" s="9" t="s">
+        <v>9</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>92</v>
+        <v>113</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="B70" s="14" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C70" s="6" t="s">
         <v>2</v>
@@ -1752,12 +1976,12 @@
         <v>11</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>98</v>
+        <v>120</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="B71" s="5" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C71" s="6" t="s">
         <v>61</v>
@@ -1771,7 +1995,7 @@
     </row>
     <row r="72" spans="1:5" ht="27">
       <c r="B72" s="5" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C72" s="6" t="s">
         <v>61</v>
@@ -1780,26 +2004,26 @@
         <v>11</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>66</v>
+        <v>125</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="B73" s="5" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C73" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D73" s="8" t="s">
-        <v>11</v>
+      <c r="D73" s="19" t="s">
+        <v>112</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>79</v>
+        <v>124</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="B74" s="5" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C74" s="6" t="s">
         <v>10</v>
@@ -1808,12 +2032,12 @@
         <v>11</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="B75" s="5" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C75" s="6" t="s">
         <v>61</v>
@@ -1822,12 +2046,12 @@
         <v>22</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="B76" s="5" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C76" s="6" t="s">
         <v>61</v>
@@ -1836,12 +2060,12 @@
         <v>22</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="77" spans="1:5" ht="40.5">
       <c r="B77" s="5" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C77" s="6" t="s">
         <v>61</v>
@@ -1850,12 +2074,12 @@
         <v>22</v>
       </c>
       <c r="E77" s="18" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="B78" s="5" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C78" s="6" t="s">
         <v>2</v>
@@ -1864,21 +2088,216 @@
         <v>22</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="B79" s="5" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C79" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D79" s="8" t="s">
-        <v>11</v>
+      <c r="D79" s="9" t="s">
+        <v>9</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>113</v>
+        <v>110</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" s="11">
+        <v>41862</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="B83" s="17" t="s">
+        <v>114</v>
+      </c>
+      <c r="C83" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D83" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
+      <c r="B84" s="17" t="s">
+        <v>116</v>
+      </c>
+      <c r="C84" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D84" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5">
+      <c r="B85" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="C85" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D85" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5">
+      <c r="B86" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="C86" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D86" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5">
+      <c r="B87" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="C87" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D87" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" ht="27">
+      <c r="B88" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="C88" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D88" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5">
+      <c r="B89" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="C89" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D89" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5">
+      <c r="B90" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C90" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D90" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5">
+      <c r="B91" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="C91" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D91" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5">
+      <c r="B92" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="C92" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D92" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" ht="40.5">
+      <c r="B93" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="C93" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D93" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E93" s="18" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5">
+      <c r="B94" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="C94" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D94" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E94" s="21" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5">
+      <c r="B95" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="C95" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D95" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5">
+      <c r="B96" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="C96" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D96" s="10" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -1887,9 +2306,10 @@
     <hyperlink ref="E46" r:id="rId1" display="http://jira:8080/browse/SEQUOIADBMAINSTREAM-257"/>
     <hyperlink ref="E45" r:id="rId2" display="http://jira:8080/browse/SEQUOIADBMAINSTREAM-264"/>
     <hyperlink ref="E77" r:id="rId3"/>
+    <hyperlink ref="E93" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId4"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId5"/>
 </worksheet>
 </file>
 
@@ -1898,7 +2318,7 @@
   <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="16.75" customWidth="1"/>
+    <col min="2" max="2" width="37.125" customWidth="1"/>
     <col min="4" max="4" width="10.75" customWidth="1"/>
     <col min="5" max="5" width="26.25" customWidth="1"/>
   </cols>
@@ -1909,20 +2329,22 @@
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="B2" t="s">
-        <v>85</v>
-      </c>
-      <c r="D2" s="4"/>
+      <c r="B2" s="20" t="s">
+        <v>122</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="3" spans="1:4">
       <c r="B3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D3" s="4"/>
     </row>
     <row r="4" spans="1:4">
       <c r="B4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D4" s="4"/>
     </row>

--- a/testprocess/1-process/db-test-plan.xlsx
+++ b/testprocess/1-process/db-test-plan.xlsx
@@ -2229,8 +2229,8 @@
       <c r="C91" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="D91" s="8" t="s">
-        <v>11</v>
+      <c r="D91" s="9" t="s">
+        <v>9</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>127</v>

--- a/testprocess/1-process/db-test-plan.xlsx
+++ b/testprocess/1-process/db-test-plan.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="139">
   <si>
     <t>主要进行1.8版本功能测试</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -635,6 +635,38 @@
   </si>
   <si>
     <t>14.CI集成rpm包</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>简单实验了下rpm包的安装，但是由于没有将rmp包作为一个系统的工程完成，因此没有进行规范化测试。此工作暂停。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9.CI中驱动用例需要在集群环境下运行</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10.ant测试用例缺少sdbkillmasternode</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11.sdbsupport工具能否对外提供使用</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12.rpm安装包测试</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13.CI集成rpm包</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>14.mongodb的gridFS操作</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>主要是为了后续进行lob性能测试对比。目前完成通过java程序操作gridFS，还需要完成通过c++驱动操作gridFS</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1232,7 +1264,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E96"/>
+  <dimension ref="A1:E113"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="11.625" style="2" customWidth="1"/>
@@ -2285,8 +2317,11 @@
       <c r="C95" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D95" s="8" t="s">
-        <v>11</v>
+      <c r="D95" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="96" spans="1:5">
@@ -2298,6 +2333,204 @@
       </c>
       <c r="D96" s="10" t="s">
         <v>22</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5">
+      <c r="A99" s="11">
+        <v>41869</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5">
+      <c r="B100" s="17" t="s">
+        <v>114</v>
+      </c>
+      <c r="C100" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D100" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5">
+      <c r="B101" s="17" t="s">
+        <v>116</v>
+      </c>
+      <c r="C101" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D101" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5">
+      <c r="B102" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="C102" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D102" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5">
+      <c r="B103" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="C103" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D103" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E103" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5">
+      <c r="B104" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="C104" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D104" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E104" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" ht="27">
+      <c r="B105" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="C105" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D105" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="E105" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5">
+      <c r="B106" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="C106" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D106" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="E106" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5">
+      <c r="B107" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C107" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D107" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E107" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5">
+      <c r="B108" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="C108" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D108" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E108" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" ht="40.5">
+      <c r="B109" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="C109" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D109" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E109" s="18" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5">
+      <c r="B110" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="C110" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D110" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E110" s="21" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5">
+      <c r="B111" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="C111" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D111" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="E111" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5">
+      <c r="B112" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="C112" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D112" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="113" spans="2:5">
+      <c r="B113" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="C113" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D113" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E113" s="2" t="s">
+        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -2307,9 +2540,10 @@
     <hyperlink ref="E45" r:id="rId2" display="http://jira:8080/browse/SEQUOIADBMAINSTREAM-264"/>
     <hyperlink ref="E77" r:id="rId3"/>
     <hyperlink ref="E93" r:id="rId4"/>
+    <hyperlink ref="E109" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId6"/>
 </worksheet>
 </file>
 

--- a/testprocess/1-process/db-test-plan.xlsx
+++ b/testprocess/1-process/db-test-plan.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="142">
   <si>
     <t>主要进行1.8版本功能测试</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -642,31 +642,43 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>9.CI中驱动用例需要在集群环境下运行</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10.ant测试用例缺少sdbkillmasternode</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>11.sdbsupport工具能否对外提供使用</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>12.rpm安装包测试</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>13.CI集成rpm包</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>14.mongodb的gridFS操作</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>主要是为了后续进行lob性能测试对比。目前完成通过java程序操作gridFS，还需要完成通过c++驱动操作gridFS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5.ci改进：整体测试活动中，无关系的构建项目应该不会彼此受到影响</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6.有关场景测试计划和设计</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7.CI中js测试用例错误定位、修改</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8.CI中驱动用例需要在集群环境下运行</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9.ant测试用例缺少sdbkillmasternode</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10.sdbsupport工具能否对外提供使用</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11.rpm安装包测试</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12.CI集成rpm包</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13.mongodb的gridFS操作</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1264,7 +1276,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E113"/>
+  <dimension ref="A1:E112"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="11.625" style="2" customWidth="1"/>
@@ -2205,8 +2217,8 @@
       <c r="C87" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="D87" s="8" t="s">
-        <v>11</v>
+      <c r="D87" s="9" t="s">
+        <v>9</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>123</v>
@@ -2396,65 +2408,65 @@
         <v>121</v>
       </c>
     </row>
-    <row r="104" spans="1:5">
+    <row r="104" spans="1:5" ht="27">
       <c r="B104" s="5" t="s">
-        <v>96</v>
+        <v>133</v>
       </c>
       <c r="C104" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="D104" s="8" t="s">
-        <v>11</v>
+      <c r="D104" s="19" t="s">
+        <v>112</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="105" spans="1:5" ht="27">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5">
       <c r="B105" s="5" t="s">
-        <v>97</v>
+        <v>134</v>
       </c>
       <c r="C105" s="6" t="s">
-        <v>61</v>
+        <v>10</v>
       </c>
       <c r="D105" s="19" t="s">
         <v>112</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="B106" s="5" t="s">
-        <v>98</v>
+        <v>135</v>
       </c>
       <c r="C106" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D106" s="19" t="s">
-        <v>112</v>
+      <c r="D106" s="8" t="s">
+        <v>11</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="B107" s="5" t="s">
-        <v>99</v>
+        <v>136</v>
       </c>
       <c r="C107" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D107" s="8" t="s">
-        <v>11</v>
+        <v>61</v>
+      </c>
+      <c r="D107" s="10" t="s">
+        <v>22</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" ht="40.5">
       <c r="B108" s="5" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="C108" s="6" t="s">
         <v>61</v>
@@ -2462,75 +2474,61 @@
       <c r="D108" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="E108" s="2" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5" ht="40.5">
+      <c r="E108" s="18" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5">
       <c r="B109" s="5" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="C109" s="6" t="s">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="D109" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="E109" s="18" t="s">
-        <v>106</v>
+      <c r="E109" s="21" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="110" spans="1:5">
       <c r="B110" s="5" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="C110" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="D110" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="E110" s="21" t="s">
-        <v>128</v>
+        <v>10</v>
+      </c>
+      <c r="D110" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="E110" s="2" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="111" spans="1:5">
       <c r="B111" s="5" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="C111" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D111" s="19" t="s">
-        <v>112</v>
-      </c>
-      <c r="E111" s="2" t="s">
-        <v>131</v>
+        <v>61</v>
+      </c>
+      <c r="D111" s="10" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="112" spans="1:5">
       <c r="B112" s="5" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="C112" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="D112" s="10" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="113" spans="2:5">
-      <c r="B113" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="C113" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D113" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="E113" s="2" t="s">
-        <v>138</v>
+      <c r="D112" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E112" s="2" t="s">
+        <v>132</v>
       </c>
     </row>
   </sheetData>
@@ -2540,7 +2538,7 @@
     <hyperlink ref="E45" r:id="rId2" display="http://jira:8080/browse/SEQUOIADBMAINSTREAM-264"/>
     <hyperlink ref="E77" r:id="rId3"/>
     <hyperlink ref="E93" r:id="rId4"/>
-    <hyperlink ref="E109" r:id="rId5"/>
+    <hyperlink ref="E108" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId6"/>

--- a/testprocess/1-process/db-test-plan.xlsx
+++ b/testprocess/1-process/db-test-plan.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="169">
   <si>
     <t>主要进行1.8版本功能测试</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -679,6 +679,115 @@
   </si>
   <si>
     <t>13.mongodb的gridFS操作</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://192.168.20.11/sequoiadb/trunk/testprocess/1-process/数据一致性校验工具</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>评审完成，开始进行测试</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目前仅测试standalone模式的基本功能。集群还不支持lob功能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rpm的制作脚本主要由李建华完成。等脚本完成，移植至CI即可</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目前基本完成。先阶段错误主要为并发测试用例错误导致。胡晓均修改js测试脚本中coord、svrname常量的问题已经完成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.lob对象测试</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4.ci改进：整体测试活动中，无关系的构建项目应该不会彼此受到影响</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5.有关场景测试计划和设计</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6.CI中js测试用例错误定位、修改</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7.CI中驱动用例需要在集群环境下运行</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8.ant测试用例缺少sdbkillmasternode</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9.sdbsupport工具能否对外提供使用</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.c驱动测试</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>需要按照已有的c驱动测试框架整理新测试用例。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>预计这周可以完成测试。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6.CI中驱动用例需要在集群环境下运行</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7.ant测试用例缺少sdbkillmasternode</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8.sdbsupport工具能否对外提供使用</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11.mongodb的gridFS操作</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10.CI集成rpm包，以及rpm包测试</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>完成C++驱动操作mongo的gridFS，同时完成c驱动操作sequoiadb的lob对象。2者已经整合至一个c++程序中，可以进行性能对比测试</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12.福建移动项目的测试支持</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9.福建移动项目的测试支持</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>完成数据装载测试，hadoop连接器测试，hive连接器测试。以及explain的java驱动测试和Run:false支持测试</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10.重现连接出现close_wait的问题</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试程序很多个session（大约为1000个）连接到db，使用Ctrl+c终止测试程序。此时连接db失败。在db的服务器上查看，发现很多个db的tcp连接处于close_wait状态，导致资源不释放，无法建立新的连接。能否模拟这种情况，确认db的session释放过程是否存在问题。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://192.168.20.11/sequoiadb/trunk/testprocess/1-process/集群随机启动
+集群启动确定不同节点 有顺序和时间要求，在某些情况下启动集群是可能失败的</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -779,7 +888,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -822,6 +931,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -854,7 +969,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -912,6 +1027,12 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1276,14 +1397,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E112"/>
+  <dimension ref="A1:E140"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="11.625" style="2" customWidth="1"/>
     <col min="2" max="2" width="35.875" style="13" customWidth="1"/>
     <col min="3" max="3" width="9" style="1" customWidth="1"/>
     <col min="4" max="4" width="28.75" style="2" customWidth="1"/>
-    <col min="5" max="5" width="68.375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="72.625" style="2" customWidth="1"/>
     <col min="6" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
@@ -2387,11 +2508,11 @@
       <c r="C102" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="D102" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="E102" s="2" t="s">
-        <v>119</v>
+      <c r="D102" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E102" s="15" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="103" spans="1:5">
@@ -2401,11 +2522,11 @@
       <c r="C103" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D103" s="8" t="s">
-        <v>11</v>
+      <c r="D103" s="22" t="s">
+        <v>9</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>121</v>
+        <v>143</v>
       </c>
     </row>
     <row r="104" spans="1:5" ht="27">
@@ -2457,8 +2578,8 @@
       <c r="C107" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="D107" s="10" t="s">
-        <v>22</v>
+      <c r="D107" s="8" t="s">
+        <v>11</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>105</v>
@@ -2529,6 +2650,291 @@
       </c>
       <c r="E112" s="2" t="s">
         <v>132</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5">
+      <c r="A115" s="11">
+        <v>41876</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" ht="27">
+      <c r="B116" s="17" t="s">
+        <v>114</v>
+      </c>
+      <c r="C116" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D116" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E116" s="23" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5">
+      <c r="B117" s="17" t="s">
+        <v>116</v>
+      </c>
+      <c r="C117" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D117" s="19" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5">
+      <c r="B118" s="14" t="s">
+        <v>147</v>
+      </c>
+      <c r="C118" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D118" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E118" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" ht="27">
+      <c r="B119" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="C119" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D119" s="19" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5">
+      <c r="B120" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="C120" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D120" s="19" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5">
+      <c r="B121" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="C121" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D121" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E121" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5">
+      <c r="B122" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="C122" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D122" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5">
+      <c r="B123" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="C123" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D123" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5">
+      <c r="B124" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="C124" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D124" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E124" s="21" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5">
+      <c r="B125" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="C125" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D125" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E125" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" ht="27">
+      <c r="B126" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="C126" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D126" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E126" s="13" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5">
+      <c r="B127" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="C127" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D127" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5">
+      <c r="A130" s="11">
+        <v>41883</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5">
+      <c r="B131" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="C131" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D131" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E131" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5">
+      <c r="B132" s="17" t="s">
+        <v>116</v>
+      </c>
+      <c r="C132" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D132" s="19" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5">
+      <c r="B133" s="14" t="s">
+        <v>147</v>
+      </c>
+      <c r="C133" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D133" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E133" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" ht="27">
+      <c r="B134" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="C134" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D134" s="19" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5">
+      <c r="B135" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="C135" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D135" s="19" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5">
+      <c r="B136" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="C136" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D136" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5">
+      <c r="B137" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="C137" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D137" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5">
+      <c r="B138" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="C138" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D138" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E138" s="21" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5">
+      <c r="B139" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="C139" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D139" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E139" s="2" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" ht="54">
+      <c r="B140" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="C140" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D140" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E140" s="13" t="s">
+        <v>167</v>
       </c>
     </row>
   </sheetData>
@@ -2539,9 +2945,11 @@
     <hyperlink ref="E77" r:id="rId3"/>
     <hyperlink ref="E93" r:id="rId4"/>
     <hyperlink ref="E108" r:id="rId5"/>
+    <hyperlink ref="E116" r:id="rId6"/>
+    <hyperlink ref="E102" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId6"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId8"/>
 </worksheet>
 </file>
 

--- a/testprocess/1-process/db-test-plan.xlsx
+++ b/testprocess/1-process/db-test-plan.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="170">
   <si>
     <t>主要进行1.8版本功能测试</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -788,6 +788,10 @@
   <si>
     <t>http://192.168.20.11/sequoiadb/trunk/testprocess/1-process/集群随机启动
 集群启动确定不同节点 有顺序和时间要求，在某些情况下启动集群是可能失败的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9.重现连接出现close_wait的问题</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1397,7 +1401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E140"/>
+  <dimension ref="A1:E152"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="11.625" style="2" customWidth="1"/>
@@ -2934,6 +2938,122 @@
         <v>11</v>
       </c>
       <c r="E140" s="13" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5">
+      <c r="A143" s="11">
+        <v>41891</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5">
+      <c r="B144" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="C144" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D144" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E144" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="145" spans="2:5">
+      <c r="B145" s="17" t="s">
+        <v>116</v>
+      </c>
+      <c r="C145" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D145" s="19" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="146" spans="2:5">
+      <c r="B146" s="14" t="s">
+        <v>147</v>
+      </c>
+      <c r="C146" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D146" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E146" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="147" spans="2:5" ht="27">
+      <c r="B147" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="C147" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D147" s="19" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="148" spans="2:5">
+      <c r="B148" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="C148" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D148" s="19" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="149" spans="2:5">
+      <c r="B149" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="C149" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D149" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="150" spans="2:5">
+      <c r="B150" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="C150" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D150" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="151" spans="2:5">
+      <c r="B151" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="C151" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D151" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E151" s="21" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="152" spans="2:5" ht="54">
+      <c r="B152" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="C152" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D152" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E152" s="13" t="s">
         <v>167</v>
       </c>
     </row>

--- a/testprocess/1-process/db-test-plan.xlsx
+++ b/testprocess/1-process/db-test-plan.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="184">
   <si>
     <t>主要进行1.8版本功能测试</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -792,6 +792,76 @@
   </si>
   <si>
     <t>9.重现连接出现close_wait的问题</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>需要按照已有的c驱动测试框架整理新测试用例。优先完成sdblist工具开发</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10.sdblist开发任务</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SEQUOIADBMAINSTREAM-329</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">测试程序很多个session（大约为1000个）连接到db，使用Ctrl+c终止测试程序。此时连接db失败。在db的服务器上查看，发现很多个db的tcp连接处于close_wait状态，导致资源不释放，无法建立新的连接。能否模拟这种情况，确认db的session释放过程是否存在问题。
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>此种情况需要在机器压力极大，进程无法及时处理异常断开的socket连接时才可能出现。但是常规模拟机器负载压力大多线程连接读写没有重现</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11.forceSession功能测试</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>暂时忽略该问题。目前没有影响测试</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>完成单机功能的测试。完成情景模拟：小于16M图片直接以binary存储于db，大于16M图片以lob形式存储</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目前驱动测试用例已经在单机和集群下运行。Php测试用例有未过的，还没有处理</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>未完成，但结束该任务</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4.ci改进：部分测试并发执行</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12.CI中PG测试程序更换为JAVA版本程序</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>完成部分功能，目前js测试用例并发执行。后续可以考虑场景之间的并发。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SEQUOIADBMAINSTREAM-329，代码不合规范，需要重写</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.lob对象测试</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -892,7 +962,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -941,6 +1011,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -973,7 +1049,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1037,6 +1113,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1401,7 +1480,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E152"/>
+  <dimension ref="A1:E167"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="11.625" style="2" customWidth="1"/>
@@ -2953,14 +3032,14 @@
       <c r="C144" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="D144" s="8" t="s">
-        <v>11</v>
+      <c r="D144" s="19" t="s">
+        <v>112</v>
       </c>
       <c r="E144" s="2" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="145" spans="2:5">
+    <row r="145" spans="1:5">
       <c r="B145" s="17" t="s">
         <v>116</v>
       </c>
@@ -2971,7 +3050,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="146" spans="2:5">
+    <row r="146" spans="1:5">
       <c r="B146" s="14" t="s">
         <v>147</v>
       </c>
@@ -2985,18 +3064,18 @@
         <v>156</v>
       </c>
     </row>
-    <row r="147" spans="2:5" ht="27">
+    <row r="147" spans="1:5">
       <c r="B147" s="5" t="s">
-        <v>148</v>
+        <v>179</v>
       </c>
       <c r="C147" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="D147" s="19" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="148" spans="2:5">
+      <c r="D147" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5">
       <c r="B148" s="5" t="s">
         <v>149</v>
       </c>
@@ -3007,18 +3086,21 @@
         <v>112</v>
       </c>
     </row>
-    <row r="149" spans="2:5">
+    <row r="149" spans="1:5">
       <c r="B149" s="5" t="s">
         <v>157</v>
       </c>
       <c r="C149" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="D149" s="10" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="150" spans="2:5">
+      <c r="D149" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E149" s="2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5">
       <c r="B150" s="5" t="s">
         <v>158</v>
       </c>
@@ -3029,7 +3111,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="151" spans="2:5">
+    <row r="151" spans="1:5">
       <c r="B151" s="5" t="s">
         <v>159</v>
       </c>
@@ -3043,7 +3125,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="152" spans="2:5" ht="54">
+    <row r="152" spans="1:5" ht="54">
       <c r="B152" s="5" t="s">
         <v>169</v>
       </c>
@@ -3055,6 +3137,167 @@
       </c>
       <c r="E152" s="13" t="s">
         <v>167</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5">
+      <c r="B153" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="C153" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D153" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E153" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5">
+      <c r="A156" s="11">
+        <v>41897</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5">
+      <c r="B157" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="C157" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D157" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="E157" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5">
+      <c r="B158" s="17" t="s">
+        <v>116</v>
+      </c>
+      <c r="C158" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D158" s="19" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5">
+      <c r="B159" s="14" t="s">
+        <v>183</v>
+      </c>
+      <c r="C159" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D159" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E159" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5">
+      <c r="B160" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="C160" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D160" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E160" s="2" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="161" spans="2:5">
+      <c r="B161" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="C161" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D161" s="19" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="162" spans="2:5">
+      <c r="B162" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="C162" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D162" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E162" s="2" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="163" spans="2:5">
+      <c r="B163" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="C163" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D163" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E163" s="21" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="164" spans="2:5" ht="81">
+      <c r="B164" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="C164" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D164" s="24" t="s">
+        <v>178</v>
+      </c>
+      <c r="E164" s="13" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="165" spans="2:5">
+      <c r="B165" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="C165" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D165" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E165" s="2" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="166" spans="2:5">
+      <c r="B166" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="C166" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D166" s="22" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="167" spans="2:5">
+      <c r="B167" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="C167" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D167" s="8" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/testprocess/1-process/db-test-plan.xlsx
+++ b/testprocess/1-process/db-test-plan.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="195">
   <si>
     <t>主要进行1.8版本功能测试</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -845,10 +845,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>4.ci改进：部分测试并发执行</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>12.CI中PG测试程序更换为JAVA版本程序</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -862,6 +858,54 @@
   </si>
   <si>
     <t>3.lob对象测试</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.lob对象集群功能测试</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lob集群功能测试的前期准备工作</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4.ci改进：部分测试场景并发执行</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4.ci改进：部分测试用例并发执行</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5.ci改进：测试数据收集</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目前js测试用例执行完成会形成一个记录测试结果的json文件。将json文件导入数据库即完成测试数据收集。后期考虑其它类型测试用例的测试结果收集。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>这部分需要结合实际资源，考虑哪些测试场景可以并发执行。同时需要修改测试环境的部署方式。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>需要为即将开始的发版测试，设计应用场景进行场景测试。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6.ant测试用例缺少sdbkillmasternode</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7.sdbsupport工具能否对外提供使用</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8.sdblist开发任务</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9.CI中PG测试程序更换为JAVA版本程序</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1480,7 +1524,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E167"/>
+  <dimension ref="A1:E180"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="11.625" style="2" customWidth="1"/>
@@ -3066,7 +3110,7 @@
     </row>
     <row r="147" spans="1:5">
       <c r="B147" s="5" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="C147" s="6" t="s">
         <v>61</v>
@@ -3185,7 +3229,7 @@
     </row>
     <row r="159" spans="1:5">
       <c r="B159" s="14" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C159" s="6" t="s">
         <v>2</v>
@@ -3199,7 +3243,7 @@
     </row>
     <row r="160" spans="1:5">
       <c r="B160" s="5" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="C160" s="6" t="s">
         <v>61</v>
@@ -3208,95 +3252,234 @@
         <v>9</v>
       </c>
       <c r="E160" s="2" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="161" spans="2:5">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5">
       <c r="B161" s="5" t="s">
-        <v>149</v>
+        <v>187</v>
       </c>
       <c r="C161" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D161" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E161" s="2" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5">
+      <c r="B162" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="C162" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D161" s="19" t="s">
+      <c r="D162" s="19" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="162" spans="2:5">
-      <c r="B162" s="5" t="s">
+    <row r="163" spans="1:5">
+      <c r="B163" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="C162" s="6" t="s">
+      <c r="C163" s="6" t="s">
         <v>61</v>
-      </c>
-      <c r="D162" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="E162" s="2" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="163" spans="2:5">
-      <c r="B163" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="C163" s="6" t="s">
-        <v>2</v>
       </c>
       <c r="D163" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="E163" s="21" t="s">
+      <c r="E163" s="2" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5">
+      <c r="B164" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="C164" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D164" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E164" s="21" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="164" spans="2:5" ht="81">
-      <c r="B164" s="5" t="s">
+    <row r="165" spans="1:5" ht="81">
+      <c r="B165" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="C164" s="6" t="s">
+      <c r="C165" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D164" s="24" t="s">
+      <c r="D165" s="24" t="s">
         <v>178</v>
       </c>
-      <c r="E164" s="13" t="s">
+      <c r="E165" s="13" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="165" spans="2:5">
-      <c r="B165" s="5" t="s">
+    <row r="166" spans="1:5">
+      <c r="B166" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="C165" s="6" t="s">
+      <c r="C166" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="D165" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="E165" s="2" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="166" spans="2:5">
-      <c r="B166" s="5" t="s">
+      <c r="D166" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E166" s="2" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5">
+      <c r="B167" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="C166" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="D166" s="22" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="167" spans="2:5">
-      <c r="B167" s="5" t="s">
-        <v>180</v>
-      </c>
       <c r="C167" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D167" s="22" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5">
+      <c r="B168" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="C168" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="D167" s="8" t="s">
+      <c r="D168" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5">
+      <c r="A171" s="11">
+        <v>41904</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5">
+      <c r="B172" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="C172" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D172" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="E172" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5">
+      <c r="B173" s="17" t="s">
+        <v>116</v>
+      </c>
+      <c r="C173" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D173" s="19" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5">
+      <c r="B174" s="14" t="s">
+        <v>183</v>
+      </c>
+      <c r="C174" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D174" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E174" s="2" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5">
+      <c r="B175" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="C175" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D175" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E175" s="2" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5">
+      <c r="B176" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="C176" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D176" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E176" s="2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="177" spans="2:5">
+      <c r="B177" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="C177" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D177" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E177" s="2" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="178" spans="2:5">
+      <c r="B178" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="C178" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D178" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E178" s="21" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="179" spans="2:5">
+      <c r="B179" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="C179" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D179" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E179" s="2" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="180" spans="2:5">
+      <c r="B180" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="C180" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D180" s="8" t="s">
         <v>11</v>
       </c>
     </row>

--- a/testprocess/1-process/db-test-plan.xlsx
+++ b/testprocess/1-process/db-test-plan.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="573" uniqueCount="198">
   <si>
     <t>主要进行1.8版本功能测试</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -906,6 +906,18 @@
   </si>
   <si>
     <t>9.CI中PG测试程序更换为JAVA版本程序</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试完成。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10.CI测试：YCSB部署自动化测试</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lob集群功能测试</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1524,7 +1536,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E180"/>
+  <dimension ref="A1:E193"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="11.625" style="2" customWidth="1"/>
@@ -3430,7 +3442,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="177" spans="2:5">
+    <row r="177" spans="1:5">
       <c r="B177" s="5" t="s">
         <v>191</v>
       </c>
@@ -3444,7 +3456,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="178" spans="2:5">
+    <row r="178" spans="1:5">
       <c r="B178" s="5" t="s">
         <v>192</v>
       </c>
@@ -3458,7 +3470,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="179" spans="2:5">
+    <row r="179" spans="1:5">
       <c r="B179" s="5" t="s">
         <v>193</v>
       </c>
@@ -3472,7 +3484,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="180" spans="2:5">
+    <row r="180" spans="1:5">
       <c r="B180" s="5" t="s">
         <v>194</v>
       </c>
@@ -3481,6 +3493,142 @@
       </c>
       <c r="D180" s="8" t="s">
         <v>11</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5">
+      <c r="A183" s="11">
+        <v>41911</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5">
+      <c r="B184" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="C184" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D184" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="E184" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5">
+      <c r="B185" s="17" t="s">
+        <v>116</v>
+      </c>
+      <c r="C185" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D185" s="19" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5">
+      <c r="B186" s="14" t="s">
+        <v>183</v>
+      </c>
+      <c r="C186" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D186" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E186" s="2" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5">
+      <c r="B187" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="C187" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D187" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E187" s="2" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5">
+      <c r="B188" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="C188" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D188" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E188" s="2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5">
+      <c r="B189" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="C189" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D189" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E189" s="2" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5">
+      <c r="B190" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="C190" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D190" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E190" s="21" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5">
+      <c r="B191" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="C191" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D191" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E191" s="2" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5">
+      <c r="B192" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="C192" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D192" s="22" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="193" spans="2:4">
+      <c r="B193" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="C193" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D193" s="19" t="s">
+        <v>112</v>
       </c>
     </row>
   </sheetData>

--- a/testprocess/1-process/db-test-plan.xlsx
+++ b/testprocess/1-process/db-test-plan.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="573" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="200">
   <si>
     <t>主要进行1.8版本功能测试</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -920,12 +920,72 @@
     <t>lob集群功能测试</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>安装包已经包含</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="0" tint="-0.499984740745262"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>信息中心文档没有使用说明</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>jira中问题已经关闭</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8.CI测试：YCSB部署自动化测试</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1012,6 +1072,14 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0" tint="-0.499984740745262"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
@@ -1536,10 +1604,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E193"/>
+  <dimension ref="A1:E207"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="11.625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="13.125" style="2" customWidth="1"/>
     <col min="2" max="2" width="35.875" style="13" customWidth="1"/>
     <col min="3" max="3" width="9" style="1" customWidth="1"/>
     <col min="4" max="4" width="28.75" style="2" customWidth="1"/>
@@ -3620,7 +3688,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="193" spans="2:4">
+    <row r="193" spans="1:5">
       <c r="B193" s="5" t="s">
         <v>196</v>
       </c>
@@ -3629,6 +3697,119 @@
       </c>
       <c r="D193" s="19" t="s">
         <v>112</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5">
+      <c r="A196" s="11">
+        <v>41925</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5">
+      <c r="B197" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="C197" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D197" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5">
+      <c r="B198" s="17" t="s">
+        <v>116</v>
+      </c>
+      <c r="C198" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D198" s="19" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5">
+      <c r="B199" s="14" t="s">
+        <v>183</v>
+      </c>
+      <c r="C199" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D199" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E199" s="2" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5">
+      <c r="B200" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="C200" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D200" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E200" s="2" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5">
+      <c r="B201" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="C201" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D201" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E201" s="2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5">
+      <c r="B202" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="C202" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D202" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E202" s="2" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5">
+      <c r="B203" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="C203" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D203" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E203" s="21" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5">
+      <c r="B204" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="C204" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D204" s="19" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5">
+      <c r="A207" s="11">
+        <v>41932</v>
       </c>
     </row>
   </sheetData>

--- a/testprocess/1-process/db-test-plan.xlsx
+++ b/testprocess/1-process/db-test-plan.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="639" uniqueCount="209">
   <si>
     <t>主要进行1.8版本功能测试</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -978,6 +978,42 @@
   </si>
   <si>
     <t>8.CI测试：YCSB部署自动化测试</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4.CI：om安装包制作</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7.lob驱动测试用例编写（包括java、c++、python）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>这周主要测试待发布版本</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>这个版本需要提供java、c++、python的lob接口，目前已经完成。需要补充简单的测试用例保证这些接口可用</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9.jira单整理</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>整理还未关闭的jira单</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10.文档检查</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>这个版本添加了不少接口，工具也进行了改进，所以文档也需要同步更新</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11.新版本测试跟踪</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1604,7 +1640,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E207"/>
+  <dimension ref="A1:E218"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="13.125" style="2" customWidth="1"/>
@@ -3761,8 +3797,8 @@
       <c r="C201" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D201" s="8" t="s">
-        <v>11</v>
+      <c r="D201" s="19" t="s">
+        <v>112</v>
       </c>
       <c r="E201" s="2" t="s">
         <v>190</v>
@@ -3810,6 +3846,139 @@
     <row r="207" spans="1:5">
       <c r="A207" s="11">
         <v>41932</v>
+      </c>
+      <c r="B207" s="13" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5">
+      <c r="B208" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="C208" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D208" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="209" spans="2:5">
+      <c r="B209" s="17" t="s">
+        <v>116</v>
+      </c>
+      <c r="C209" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D209" s="19" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="210" spans="2:5">
+      <c r="B210" s="14" t="s">
+        <v>183</v>
+      </c>
+      <c r="C210" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D210" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="211" spans="2:5">
+      <c r="B211" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="C211" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D211" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="212" spans="2:5">
+      <c r="B212" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="C212" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D212" s="19" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="213" spans="2:5">
+      <c r="B213" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="C213" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D213" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="214" spans="2:5" ht="40.5">
+      <c r="B214" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="C214" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D214" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E214" s="2" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="215" spans="2:5">
+      <c r="B215" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="C215" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D215" s="19" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="216" spans="2:5">
+      <c r="B216" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="C216" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D216" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E216" s="2" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="217" spans="2:5">
+      <c r="B217" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="C217" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D217" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E217" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="218" spans="2:5">
+      <c r="B218" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="C218" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D218" s="8" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/testprocess/1-process/db-test-plan.xlsx
+++ b/testprocess/1-process/db-test-plan.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="639" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="710" uniqueCount="236">
   <si>
     <t>主要进行1.8版本功能测试</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -993,10 +993,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>这个版本需要提供java、c++、python的lob接口，目前已经完成。需要补充简单的测试用例保证这些接口可用</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>9.jira单整理</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1005,15 +1001,147 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>10.文档检查</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>这个版本添加了不少接口，工具也进行了改进，所以文档也需要同步更新</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>11.新版本测试跟踪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>新添加接口没有补充测试用例</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>需要将om安装过程集成至sequoiadb中，不需要单独处理</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="0" tint="-0.499984740745262"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>python、C++、java</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（java中只有开发人员简单的测试用例）</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.组的添加/删除</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>jira-130</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4.om测试</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7.补充lob的java测试用例</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>丁普升</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10.新功能文档检查</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>检查信息中心是否对新功能增加文档信息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>om安装配置集群测试。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>现有的java-lob测试用例太简单了，需要补充完善</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10.兼容性测试</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>主要是1.10版本能否直接使用1.8版本数据</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12.pg对接兼容</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>龙阳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.8与1.10的pgsql驱动互相兼容</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13.hadoop、hive对接测试</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>由高胜杰执行</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>14.文档审核--监控</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11.1.10版本测试跟踪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12.1.10版本性能测试</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>王文净</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15.1.10版本性能测试</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>17.故障恢复测试</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16.备份还原测试</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>18.context残留问题</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>jira-24</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>19.监控管理</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>包括文档检查、监控部署、监控信息等</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1021,7 +1149,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1050,6 +1178,7 @@
       <sz val="11"/>
       <color theme="10"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1116,6 +1245,13 @@
     <font>
       <sz val="11"/>
       <color theme="0" tint="-0.499984740745262"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
@@ -1640,7 +1776,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E218"/>
+  <dimension ref="A1:E241"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="13.125" style="2" customWidth="1"/>
@@ -3858,11 +3994,14 @@
       <c r="C208" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="D208" s="8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="209" spans="2:5">
+      <c r="D208" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E208" s="2" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5">
       <c r="B209" s="17" t="s">
         <v>116</v>
       </c>
@@ -3873,7 +4012,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="210" spans="2:5">
+    <row r="210" spans="1:5">
       <c r="B210" s="14" t="s">
         <v>183</v>
       </c>
@@ -3884,18 +4023,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="211" spans="2:5">
+    <row r="211" spans="1:5">
       <c r="B211" s="5" t="s">
         <v>200</v>
       </c>
       <c r="C211" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="D211" s="8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="212" spans="2:5">
+      <c r="D211" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E211" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="212" spans="1:5">
       <c r="B212" s="5" t="s">
         <v>149</v>
       </c>
@@ -3906,7 +4048,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="213" spans="2:5">
+    <row r="213" spans="1:5">
       <c r="B213" s="5" t="s">
         <v>191</v>
       </c>
@@ -3917,21 +4059,21 @@
         <v>22</v>
       </c>
     </row>
-    <row r="214" spans="2:5" ht="40.5">
+    <row r="214" spans="1:5" ht="40.5">
       <c r="B214" s="5" t="s">
         <v>201</v>
       </c>
       <c r="C214" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D214" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="E214" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="215" spans="2:5">
+      <c r="D214" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E214" s="21" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5">
       <c r="B215" s="5" t="s">
         <v>199</v>
       </c>
@@ -3942,43 +4084,295 @@
         <v>112</v>
       </c>
     </row>
-    <row r="216" spans="2:5">
+    <row r="216" spans="1:5">
       <c r="B216" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C216" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D216" s="8" t="s">
-        <v>11</v>
+      <c r="D216" s="22" t="s">
+        <v>9</v>
       </c>
       <c r="E216" s="2" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="217" spans="2:5">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5">
       <c r="B217" s="5" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="C217" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D217" s="8" t="s">
-        <v>11</v>
+      <c r="D217" s="22" t="s">
+        <v>9</v>
       </c>
       <c r="E217" s="2" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="218" spans="2:5">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="218" spans="1:5">
       <c r="B218" s="5" t="s">
-        <v>208</v>
+        <v>226</v>
       </c>
       <c r="C218" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D218" s="8" t="s">
         <v>11</v>
+      </c>
+    </row>
+    <row r="219" spans="1:5">
+      <c r="B219" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="C219" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="D219" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="222" spans="1:5">
+      <c r="A222" s="11">
+        <v>41939</v>
+      </c>
+      <c r="B222" s="13" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="223" spans="1:5">
+      <c r="B223" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="C223" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D223" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E223" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="224" spans="1:5">
+      <c r="B224" s="17" t="s">
+        <v>116</v>
+      </c>
+      <c r="C224" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D224" s="19" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="225" spans="2:5">
+      <c r="B225" s="14" t="s">
+        <v>183</v>
+      </c>
+      <c r="C225" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D225" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="226" spans="2:5">
+      <c r="B226" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="C226" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D226" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E226" s="2" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="227" spans="2:5">
+      <c r="B227" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="C227" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D227" s="19" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="228" spans="2:5">
+      <c r="B228" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="C228" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D228" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="229" spans="2:5">
+      <c r="B229" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="C229" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="D229" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E229" s="2" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="230" spans="2:5">
+      <c r="B230" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="C230" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D230" s="19" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="231" spans="2:5">
+      <c r="B231" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="C231" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D231" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="232" spans="2:5">
+      <c r="B232" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="C232" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D232" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E232" s="2" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="233" spans="2:5">
+      <c r="B233" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="C233" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D233" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="234" spans="2:5">
+      <c r="B234" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="C234" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="D234" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E234" s="2" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="235" spans="2:5">
+      <c r="B235" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="C235" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D235" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E235" s="2" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="236" spans="2:5">
+      <c r="B236" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="C236" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D236" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="237" spans="2:5">
+      <c r="B237" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="C237" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="D237" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="238" spans="2:5">
+      <c r="B238" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="C238" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D238" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="239" spans="2:5">
+      <c r="B239" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="C239" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D239" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="240" spans="2:5">
+      <c r="B240" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="C240" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D240" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E240" s="2" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="241" spans="2:5">
+      <c r="B241" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="C241" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D241" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E241" s="2" t="s">
+        <v>235</v>
       </c>
     </row>
   </sheetData>

--- a/testprocess/1-process/db-test-plan.xlsx
+++ b/testprocess/1-process/db-test-plan.xlsx
@@ -1133,15 +1133,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>jira-24</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>19.监控管理</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>包括文档检查、监控部署、监控信息等</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>jira-24（目前仅设计简单场景，没有重现这个问题，日后需要尝试更复杂场景）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4149,8 +4149,8 @@
       <c r="C223" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="D223" s="8" t="s">
-        <v>11</v>
+      <c r="D223" s="22" t="s">
+        <v>9</v>
       </c>
       <c r="E223" s="2" t="s">
         <v>210</v>
@@ -4174,8 +4174,8 @@
       <c r="C225" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D225" s="8" t="s">
-        <v>11</v>
+      <c r="D225" s="22" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="226" spans="2:5">
@@ -4185,8 +4185,8 @@
       <c r="C226" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="D226" s="8" t="s">
-        <v>11</v>
+      <c r="D226" s="22" t="s">
+        <v>9</v>
       </c>
       <c r="E226" s="2" t="s">
         <v>216</v>
@@ -4221,8 +4221,8 @@
       <c r="C229" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="D229" s="8" t="s">
-        <v>11</v>
+      <c r="D229" s="22" t="s">
+        <v>9</v>
       </c>
       <c r="E229" s="2" t="s">
         <v>217</v>
@@ -4246,8 +4246,8 @@
       <c r="C231" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D231" s="8" t="s">
-        <v>11</v>
+      <c r="D231" s="22" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="232" spans="2:5">
@@ -4257,8 +4257,8 @@
       <c r="C232" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D232" s="8" t="s">
-        <v>11</v>
+      <c r="D232" s="22" t="s">
+        <v>9</v>
       </c>
       <c r="E232" s="2" t="s">
         <v>219</v>
@@ -4271,8 +4271,8 @@
       <c r="C233" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D233" s="8" t="s">
-        <v>11</v>
+      <c r="D233" s="22" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="234" spans="2:5">
@@ -4296,8 +4296,8 @@
       <c r="C235" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D235" s="8" t="s">
-        <v>11</v>
+      <c r="D235" s="22" t="s">
+        <v>9</v>
       </c>
       <c r="E235" s="2" t="s">
         <v>224</v>
@@ -4321,8 +4321,8 @@
       <c r="C237" s="6" t="s">
         <v>228</v>
       </c>
-      <c r="D237" s="8" t="s">
-        <v>11</v>
+      <c r="D237" s="22" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="238" spans="2:5">
@@ -4354,25 +4354,25 @@
       <c r="C240" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D240" s="8" t="s">
-        <v>11</v>
+      <c r="D240" s="22" t="s">
+        <v>9</v>
       </c>
       <c r="E240" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="241" spans="2:5">
       <c r="B241" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="C241" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D241" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E241" s="2" t="s">
         <v>234</v>
-      </c>
-      <c r="C241" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="D241" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="E241" s="2" t="s">
-        <v>235</v>
       </c>
     </row>
   </sheetData>

--- a/testprocess/1-process/db-test-plan.xlsx
+++ b/testprocess/1-process/db-test-plan.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="710" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="712" uniqueCount="238">
   <si>
     <t>主要进行1.8版本功能测试</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1142,6 +1142,14 @@
   </si>
   <si>
     <t>jira-24（目前仅设计简单场景，没有重现这个问题，日后需要尝试更复杂场景）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>由龙阳完成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>挂起</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1776,7 +1784,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E241"/>
+  <dimension ref="A1:E244"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="13.125" style="2" customWidth="1"/>
@@ -4210,8 +4218,11 @@
       <c r="C228" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="D228" s="10" t="s">
-        <v>22</v>
+      <c r="D228" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="E228" s="2" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="229" spans="2:5">
@@ -4310,8 +4321,11 @@
       <c r="C236" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D236" s="10" t="s">
-        <v>22</v>
+      <c r="D236" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E236" s="2" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="237" spans="2:5">
@@ -4332,8 +4346,8 @@
       <c r="C238" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D238" s="10" t="s">
-        <v>22</v>
+      <c r="D238" s="22" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="239" spans="2:5">
@@ -4341,10 +4355,10 @@
         <v>230</v>
       </c>
       <c r="C239" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D239" s="10" t="s">
-        <v>22</v>
+        <v>2</v>
+      </c>
+      <c r="D239" s="22" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="240" spans="2:5">
@@ -4361,7 +4375,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="241" spans="2:5">
+    <row r="241" spans="1:5">
       <c r="B241" s="5" t="s">
         <v>233</v>
       </c>
@@ -4373,6 +4387,11 @@
       </c>
       <c r="E241" s="2" t="s">
         <v>234</v>
+      </c>
+    </row>
+    <row r="244" spans="1:5">
+      <c r="A244" s="11">
+        <v>41946</v>
       </c>
     </row>
   </sheetData>

--- a/testprocess/1-process/db-test-plan.xlsx
+++ b/testprocess/1-process/db-test-plan.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="712" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="804" uniqueCount="262">
   <si>
     <t>主要进行1.8版本功能测试</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1150,6 +1150,103 @@
   </si>
   <si>
     <t>挂起</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.CI测试：YCSB部署自动化测试</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>挂起，没有机器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2.有关场景测试计划和设计</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.ant测试用例缺少sdbkillmasternode</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4.rolling-update</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5.CI测试：spark、hadoop的部署</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>需要高胜杰协助完成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6.CI测试：C、C++静态驱动的测试</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>以前完成的有问题，并没有实际执行静态库的测试，现在需要重做</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7.CI测试：增加CI测试报告的容错性</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>最近由于部分测试报告不正确，导致测试结束后无法查看测试结果。CI需要处理部分测试报告错误的情形</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8.CI测试：lob测试在CI上进行部署</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8.CI测试：修改ant-sdbtask.jar测试用例包</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CI测试中涉及的不同jar版本复杂，对部署维护工作造成了不少麻烦和困扰。现在想把CI中需要的多个jar合并为一个jar</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9.设计新文档架构</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>现在的信息中心不符合用户使用习惯，需要重新设计展现形式，以及寻找合适的工具自动生成文档</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10.讨论并补充测试导入导出工具</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>胡晓均</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>胡晓均
+丁普升</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>最近一段时间，客户在使用sdbimprt发现了不少问题，需要对导入导出工具进行补充测试。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6.CI测试：增加CI测试报告的容错性</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7.讨论并补充测试导入导出工具</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8.设计新文档架构</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>讨论确定sdbimprt测试程序框架。以后测试不依赖于CI</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1784,7 +1881,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E244"/>
+  <dimension ref="A1:E276"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="13.125" style="2" customWidth="1"/>
@@ -4392,6 +4489,344 @@
     <row r="244" spans="1:5">
       <c r="A244" s="11">
         <v>41946</v>
+      </c>
+    </row>
+    <row r="245" spans="1:5">
+      <c r="B245" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="C245" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D245" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="E245" s="2" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="246" spans="1:5">
+      <c r="B246" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="C246" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D246" s="19" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="247" spans="1:5">
+      <c r="B247" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="C247" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D247" s="19" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="248" spans="1:5">
+      <c r="B248" s="17" t="s">
+        <v>242</v>
+      </c>
+      <c r="C248" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D248" s="19" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="249" spans="1:5">
+      <c r="B249" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="C249" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D249" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E249" s="2" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="250" spans="1:5">
+      <c r="B250" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="C250" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D250" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E250" s="2" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="251" spans="1:5">
+      <c r="B251" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="C251" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D251" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E251" s="2" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="252" spans="1:5">
+      <c r="B252" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="C252" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D252" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="255" spans="1:5">
+      <c r="A255" s="11">
+        <v>41953</v>
+      </c>
+    </row>
+    <row r="256" spans="1:5">
+      <c r="B256" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="C256" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D256" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="E256" s="2" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="257" spans="1:5">
+      <c r="B257" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="C257" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D257" s="19" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="258" spans="1:5">
+      <c r="B258" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="C258" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D258" s="19" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="259" spans="1:5">
+      <c r="B259" s="17" t="s">
+        <v>242</v>
+      </c>
+      <c r="C259" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="D259" s="19" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="260" spans="1:5">
+      <c r="B260" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="C260" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D260" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E260" s="2" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="261" spans="1:5">
+      <c r="B261" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="C261" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D261" s="22" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="262" spans="1:5">
+      <c r="B262" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="C262" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D262" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E262" s="2" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="263" spans="1:5" ht="27">
+      <c r="B263" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="C263" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D263" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E263" s="2" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="264" spans="1:5">
+      <c r="B264" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="C264" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D264" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E264" s="2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="265" spans="1:5" ht="27">
+      <c r="B265" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="C265" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="D265" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E265" s="2" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="268" spans="1:5">
+      <c r="A268" s="11">
+        <v>41960</v>
+      </c>
+    </row>
+    <row r="269" spans="1:5">
+      <c r="B269" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="C269" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D269" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="E269" s="2" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="270" spans="1:5">
+      <c r="B270" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="C270" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D270" s="19" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="271" spans="1:5">
+      <c r="B271" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="C271" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D271" s="19" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="272" spans="1:5">
+      <c r="B272" s="17" t="s">
+        <v>242</v>
+      </c>
+      <c r="C272" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="D272" s="19" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="273" spans="2:5">
+      <c r="B273" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="C273" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D273" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E273" s="2" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="274" spans="2:5">
+      <c r="B274" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="C274" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D274" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E274" s="2" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="275" spans="2:5" ht="27">
+      <c r="B275" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="C275" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="D275" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E275" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="276" spans="2:5">
+      <c r="B276" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="C276" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D276" s="8" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
